--- a/rmonize/data_dictionary/DD_IDEFICS_P1.xlsx
+++ b/rmonize/data_dictionary/DD_IDEFICS_P1.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,17 +383,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>ID_cohort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ID of the participant</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>integer</t>
         </is>
       </c>
     </row>
@@ -413,7 +413,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>integer</t>
         </is>
       </c>
     </row>
@@ -448,12 +448,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Isced level:Maximum of both parents</t>
+          <t>Isced-1997 level:Maximum of both parents</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>integer</t>
         </is>
       </c>
     </row>
@@ -523,12 +523,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SACANA FGS D19 "Potatoes and other starchy vegetables"</t>
+          <t>Energy intake [kcal/d]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L47</t>
+          <t>POTATOES_TUB_01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SACANA FGS L47 "Based on potatoes"</t>
+          <t>Intake of starchy roots or tubers [g/d]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>POTATOES_0101</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SACANA FGS D18 "Vegetables n.s."</t>
+          <t>Potato intake [g/d]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L44c</t>
+          <t>VEGETABLES_02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SACANA FGS L44c "Mixed salad"</t>
+          <t>Vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>LEAFYVEG_0201</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SACANA FGS D17 "Pulses n.s."</t>
+          <t>Leafy vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L44</t>
+          <t>FRUITINGVEG_0202</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SACANA FGS L44 "Legumes/Vegs n.s."</t>
+          <t>Fruiting vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L46a</t>
+          <t>ROOTVEG_0203</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SACANA FGS L46a "Fish and vegetables/legumes"</t>
+          <t>Root and tuber vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>CABBAGE_0204</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SACANA FGS D20 "Fruits n.s."</t>
+          <t>Head cabbages and similar intake [g/d]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D20a</t>
+          <t>MUSHROOMS_0205</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SACANA FGS D20a "Fresh fruits"</t>
+          <t>Mushroom intake [g/d]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D16a</t>
+          <t>GRAINPODVEG_0206</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SACANA FGS D16a "Nuts and seeds"</t>
+          <t>Intake of legumes with pod [g/d]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D16b</t>
+          <t>ONION_GARLIC_0207</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SACANA FGS D16b "Olives and avocados"</t>
+          <t>Bulb vegetables (onions, garlic) intake [g/d]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>STALKVEG_0208</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SACANA FGS J "Dairy and similar"</t>
+          <t>Intake of stems/stalks eaten as vegetables [g/d]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J37a</t>
+          <t>MIXEDVEG_0209</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SACANA FGS J37a "Milk plain whole"</t>
+          <t>Intake of mixed vegetable salad or mixed green salad [g/d]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>J37b</t>
+          <t>LEGUMES_TOT_03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SACANA FGS J37b "Milk plain reduced fat"</t>
+          <t>Total legumes intake [g/d]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>J37c</t>
+          <t>FRUITS_TOT_04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SACANA FGS J37c "Chocolate milk, vanilla milk and sim"</t>
+          <t>Total fruit intake [g/d]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J37d</t>
+          <t>FRUITS_0401</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SACANA FGS  J37d "Yogurt, probiotic and other fermented milk unsweened, full fat"</t>
+          <t>Intake of fresh fruits [g/d]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>J37e</t>
+          <t>NUTS_SEEDS_0402</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SACANA FGS J37e "Yogurt, probiotic and other fermented milk unsweened, low fat"</t>
+          <t>Intake of tree nuts and seeds [g/d]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>J37f</t>
+          <t>MIXEDFRUITS_0403</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SACANA FGS J37f "Sweet Yogurt, probiotic and other fermented milk , full fat"</t>
+          <t>Intake of candied fruit/mixed fruit, canned, jarred mixed fruit and miscellaneous fruits [g/d]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>J37g</t>
+          <t>OLIVES_0404</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SACANA FGS J37g "Sweet Yogurt, probiotic and other fermented milk, low fat"</t>
+          <t>Intake of olives [g/d]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>J38a</t>
+          <t>DAIRY_05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SACANA FGS J38a "Cheese low fat and curd (unsweetened)"</t>
+          <t>Intake of milk and dairy products and milk and milk products (dairy) [g/d]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>J38</t>
+          <t>MILK_0501</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SACANA FGS  J38 "Cheese n.s."</t>
+          <t>Intake of (whole) cow and cattle milk [g/d]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>J39a</t>
+          <t>MILKBEV_0502</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SACANA FGS J39a "milk based ice-creams, desserts, (chocolate) pudding"</t>
+          <t>Intake of buttermilk, traditional buttermilk, flavoured milk, flavoured whey and milk-based drinks (as part-nature) [g/d]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>J38c</t>
+          <t>YOGURT_0503</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SACANA FGS J38c "Sweetened cheese and curd"</t>
+          <t>Intake of fermented milk products [g/d]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>J39c</t>
+          <t>CURD_0504</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SACANA FGS J39c "cream"</t>
+          <t>Intake of cheese curd, quark and cottage [g/d]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>K40b</t>
+          <t>CHEESE_0505</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SACANA FGS  K40b "Vegetal milk (soymilk, rice milk etc.)"</t>
+          <t>Intake of cheese [g/d]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>DAIRYDESSERT_0506</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SACANA FGS A "Cereals and cereal products and starchy snacks ns"</t>
+          <t>Intake of dairy dessert and similar starchy pudding [g/d]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>L43</t>
+          <t>CREAM_PROD_0507</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SACANA FGS L43 "Based on Cereals ns"</t>
+          <t>Intake of cream and cream products [g/d]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L45c</t>
+          <t>DAIRYCREAM_050701</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SACANA FGS L45c "with vegs/potatoes/cereals"</t>
+          <t>Cream intake (as part-nature) [g/d]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>NONDAIRYCREAM_050702</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SACANA FGS A04 "Pasta (any kind)"</t>
+          <t>Intake of imitation cream, non-dairy coffee creamers and dairy imitates other than milk [g/d]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>CEREAL_PROD_06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SACANA FGS A05 "rice and other cereal grains (not ready to eat) - ns"</t>
+          <t>Intake of cereals and cereal primary derivatives, cereal grains (and cereal-like grains) [g/d]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>L43a</t>
+          <t>PASTA_RICE_0602</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SACANA FGS L43a "Pasta/rice/cereals + meat/fish/eggs/cheese"</t>
+          <t>Intake of pastas and rice [g/d]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>L43b</t>
+          <t>BREAD_PROD_0603</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SACANA FGS L43b "Pasta/rice/cereals + legumes /vegetables/potatoes"</t>
+          <t>Intake of bread and bread products [g/d]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>BREAD_060301</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SACANA FGS A01 "bread,rolls and sim. ns"</t>
+          <t>Intake of bread [g/d]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A01a</t>
+          <t>CRISPBREAD_060302</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SACANA FGS A01a "bread, crispbread, rusks, roll (refined, fiber &lt;5%)"</t>
+          <t>Intake of crisp bread and rusk [g/d]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A01b</t>
+          <t>BREAKF_CEREALS_0604</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SACANA FGS A01b "bread, crispbread, rusks, roll (wholemeal fiber&gt;5%)"</t>
+          <t>Intake of breakfast cereals [g/d]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>SALT_BISCUIT_0605</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SACANA FGS A02 "breakfast cereals, corn flakes, muesli ns"</t>
+          <t>Intake of crackers and breadsticks [g/d]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>MEAT_PROD_07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SACANA FGS G "Meat and meat products"</t>
+          <t>Intake of meat and meat products [g/d]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>L42</t>
+          <t>RED_MEAT_0701</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SACANA FGS L42 "based on meat"</t>
+          <t>Intake of red meat (mammals meat) [g/d]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>L45b</t>
+          <t>BEEF_070101</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SACANA FGS L45b "with meat/fish"</t>
+          <t>Intake of cow, ox or bull fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>G29</t>
+          <t>VEAL_070102</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SACANA FGS G29 "meat (other than poultry)-ns"</t>
+          <t>Intake of calf fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>G30</t>
+          <t>PORK_070103</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SACANA FGS G30 "poultry-ns"</t>
+          <t>Intake of pig fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>G31</t>
+          <t>MUTTON_LAMB_070104</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SACANA FGS G31 "rabbit and game"</t>
+          <t>Intake of lamb and sheep meat [g/d]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>G32</t>
+          <t>POULTRY_0702</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SACANA FGS G32 "Offals"</t>
+          <t>Intake of poultry meat [g/d]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>G33</t>
+          <t>CHICKEN_070201</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SACANA FGS G33 "Processed meat,salami, processed poultry products , meat salad- ns"</t>
+          <t>Intake of chicken meat [g/d]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>TURKEY_070202</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SACANA FGS H"Finfish, shelfish and their products"</t>
+          <t>Intake of turkey meat [g/d]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>L46</t>
+          <t>DUCK_070203</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SACANA FGS L46 "Based on fish"</t>
+          <t>Intake of duck meat [g/d]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H34</t>
+          <t>PROCMEAT_0704</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SACANA FGS H34 "Fish and seafood"</t>
+          <t>Intake of processed or preserved meat [g/d]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H35</t>
+          <t>OFFALS_0705</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SACANA FGS H35 "Processed fish products"</t>
+          <t>Intake of animal offal and other slaughtering [g/d]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>FISH_SHELLFISH_08</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SACANA FGS  I "Eggs"</t>
+          <t>Intake of fish and seafood and products thereof [g/d]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>L45</t>
+          <t>FISH_0801</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SACANA FGS L45 "based on eggs"</t>
+          <t>Intake of fish (meat) [g/d]</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>CRUSTACEANS_0802</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SACANA FGS C12 "vegetable oils ns"</t>
+          <t>Intake of seafood and products thereof [g/d]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>FISH_PROD_0803</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SACANA FGS C13 "margarines and lipids of mixed origin"</t>
+          <t>Intake of processed fish [g/d]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>EGG_PROD_09</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SACANA FGS C14 "butter and animal fats"</t>
+          <t>Intake of eggs and egg products [g/d]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>FAT_10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SACANA FGS B "Sugar and sugar products"</t>
+          <t>Intake of animal and vegetable fats and oils [g/d]</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>VEGOILS_1001</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SACANA FGS B08 "Sugar, honey, jam and sweet sauces or dessert sauces"</t>
+          <t>Intake of vegetable fats and oils [g/d]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>BUTTER_1002</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SACANA FGS B10 "Chocolate ns"</t>
+          <t>Intake of butter [g/d]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>MARGARINE_1003</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SACANA FGS B09 "Confectionery (non chocolate)"</t>
+          <t>Intake of margarines and similar [g/d]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B11b</t>
+          <t>SUGAR_CONFECT_11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SACANA FGS B11b "water ice, sorbet (excluding ice cream)"</t>
+          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>HONEY_JAM_1101</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SACANA FGS A06 "Sweet bakery, biscuits, pies (sweet), cakes , sweet fritters and other confectionery"</t>
+          <t>Intake of sugars, syrups, honey and table-top sweeteners [g/d]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>CHOCOLATE_1102</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SACANA FGS E22 "water"</t>
+          <t>Intake of chocolate, chocolate products and chocolate coated confectionary [g/d]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>E23</t>
+          <t>NONCHOC_SWEETS_1103</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SACANA FGS E23 "coffee, tea, coffee surrogate, decafe, herbal - ns"</t>
+          <t>Intake of sweet bars and other formed sweet masses, candies (soft and hard) and other confectionery including breath refreshening microsweets [g/d]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>ICECREAM_1105</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SACANA FGS E24 "fruit, vegetable juices and smoothies - ns"</t>
+          <t>Intake of spoonable desserts and ice creams [g/d]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>E25</t>
+          <t>ICECREAM_MILK_110501</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SACANA FGS E25 "Soft and sweetened drinks"</t>
+          <t>Intake of milk-based ice cream [g/d]</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>SORBET_110502</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SACANA FGS F "Alcoholic beverages ns"</t>
+          <t>Sorbet intake [g/d]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>F27</t>
+          <t>WATER_ICE_110503</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SACANA FGS F27 "Wine"</t>
+          <t>Intake of water-based ice creams [g/d]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>CAKES_12</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SACANA FGS F26 "Beer and cider"</t>
+          <t>Intake of cakes and fine bakery products [g/d]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>NONALC_BEV_13</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SACANA FGS C15 "Sauces, dressing and condiments - ns"</t>
+          <t>Intake of non-alcoholic beverages [g/d]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>FRUITVEG_JUICE_1301</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SACANA FGS E21 "Bouillon - meat/fish/vegetable"</t>
+          <t>Intake of fruit and vegetable juices [g/d]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>L44a</t>
+          <t>SOFTDRINKS_1302</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SACANA FGS L44a "Soup, veloutè, LIQUID"</t>
+          <t>Intake of soft drinks [g/d]</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>L44b</t>
+          <t>HOTDRINKS_1303</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SACANA FGS L44b "Soup, veloutè, NOT LIQUID"</t>
+          <t>Intake of hot drinks and similar (coffee, cocoa, tea and herbal infusions) [g/d]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>K40a</t>
+          <t>COFFEE_130301</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SACANA FGS K40a "Vegetarian burgers, tempeh, tofu, seitan"</t>
+          <t>Coffee intake [g/d]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1943,15 +1943,375 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>K40c</t>
+          <t>TEA_130302</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SACANA FGS K40c "Soy based dessert, cakes,and similar"</t>
+          <t>Tea intake [g/d]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HERBALTEA_130303</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Intake of herbal and other non-tea infusions [g/d]</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>COFFEE_IMITATE_130304</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Intake of chicory coffee infusion and coffee imitate beverages [g/d]</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>WATER_1304</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Intake of water and water-based beverages [g/d]</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CONDIMENT_SAUCES_15</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Intake of seasoning, sauces and condiments [g/d]</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAUCES_1501</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Intake of savoury sauces [g/d]</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TOMATOSAUCE_150101</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Intake of tomato-containing cooked sauces [g/d]</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DRESSINGS_150102</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Dressing intake [g/d]</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MAYONNAISE_150103</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Intake of mayonnaise [g/d]</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>DESSERTSAUCE_150104</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Intakes of dessert sauces/toppings [g/d]</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HERBS_SPICES_1503</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Intakes of berbs, spices and similar [g/d]</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CONDIMENTS_1504</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Condiments intake [g/d]</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SOUP_BOUILLON_16</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Intake of soups and broths [g/d]</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SOUP_1601</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Intake of soups [g/d]</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BOUILLON_1602</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Intake of mixed vegetables soup, clear meat soup [g/d]</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MISCELLANEOUS_17</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Intake of miscellaneous [g/d]</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>VEG_DISHES_1700</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Intake of vegetarian products and dishes [g/d]</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SOY_PROD_1701</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Intake of soy products [g/d]</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DIET_PROD_1702</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Intake of food for weight reduction [g/d]</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
@@ -1964,7 +2324,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1983,6 +2343,11 @@
           <t>label</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1991,11 +2356,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>Missing sex</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -2006,56 +2376,76 @@
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>isced_max</t>
+          <t>sex_child</t>
         </is>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Early childhood education (and on-going education or no graduation (yet))</t>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>isced_max</t>
+          <t>sex_child</t>
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Primary education</t>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>isced_max</t>
+          <t>sex_child</t>
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lower secondary education</t>
+          <t>not specified</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -2066,11 +2456,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Upper secondary education</t>
+          <t>Pre-primary education</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2081,11 +2476,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Post-secondary non-tertiary education</t>
+          <t>Primary education</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2096,11 +2496,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Short-cycle tertiary education</t>
+          <t>Lower secondary education</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2516,96 @@
         </is>
       </c>
       <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Upper secondary education</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>isced_max</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Post-secondary non-tertiary education</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>isced_max</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>First stage of tertiary education</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>isced_max</t>
+        </is>
+      </c>
+      <c r="B13">
         <v>6</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bachelors and higher levels</t>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Second stage of tertiary education</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>isced_max</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Don't know</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>

--- a/rmonize/data_dictionary/DD_IDEFICS_P1.xlsx
+++ b/rmonize/data_dictionary/DD_IDEFICS_P1.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -463,12 +463,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>leis_activ</t>
+          <t>phys_activ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Leisure activity [hours per week]</t>
+          <t>Physical activity[hours per week]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phys_activ</t>
+          <t>bmi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Physical activity[hours per week]</t>
+          <t>Body Mass Index</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -503,12 +503,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bmi</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Body Mass Index</t>
+          <t>Energy intake [kcal/d]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>POTATOES_TUB_01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Energy intake [kcal/d]</t>
+          <t>Intake of starchy roots or tubers [g/d]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>POTATOES_TUB_01</t>
+          <t>POTATOES_0101</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Intake of starchy roots or tubers [g/d]</t>
+          <t>Potato intake [g/d]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POTATOES_0101</t>
+          <t>VEGETABLES_02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Potato intake [g/d]</t>
+          <t>Vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VEGETABLES_02</t>
+          <t>LEAFYVEG_0201</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vegetable intake [g/d]</t>
+          <t>Leafy vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LEAFYVEG_0201</t>
+          <t>FRUITINGVEG_0202</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Leafy vegetable intake [g/d]</t>
+          <t>Fruiting vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRUITINGVEG_0202</t>
+          <t>ROOTVEG_0203</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fruiting vegetable intake [g/d]</t>
+          <t>Root and tuber vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ROOTVEG_0203</t>
+          <t>CABBAGE_0204</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Root and tuber vegetable intake [g/d]</t>
+          <t>Head cabbages and similar intake [g/d]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CABBAGE_0204</t>
+          <t>MUSHROOMS_0205</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Head cabbages and similar intake [g/d]</t>
+          <t>Mushroom intake [g/d]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MUSHROOMS_0205</t>
+          <t>GRAINPODVEG_0206</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mushroom intake [g/d]</t>
+          <t>Intake of legumes with pod [g/d]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GRAINPODVEG_0206</t>
+          <t>ONION_GARLIC_0207</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Intake of legumes with pod [g/d]</t>
+          <t>Bulb vegetables (onions, garlic) intake [g/d]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ONION_GARLIC_0207</t>
+          <t>STALKVEG_0208</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulb vegetables (onions, garlic) intake [g/d]</t>
+          <t>Intake of stems/stalks eaten as vegetables [g/d]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>STALKVEG_0208</t>
+          <t>MIXEDVEG_0209</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Intake of stems/stalks eaten as vegetables [g/d]</t>
+          <t>Intake of mixed vegetable salad or mixed green salad [g/d]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIXEDVEG_0209</t>
+          <t>LEGUMES_TOT_03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Intake of mixed vegetable salad or mixed green salad [g/d]</t>
+          <t>Total legumes intake [g/d]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LEGUMES_TOT_03</t>
+          <t>FRUITS_TOT_04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Total legumes intake [g/d]</t>
+          <t>Total fruit intake [g/d]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FRUITS_TOT_04</t>
+          <t>FRUITS_0401</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Total fruit intake [g/d]</t>
+          <t>Intake of fresh fruits [g/d]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FRUITS_0401</t>
+          <t>NUTS_SEEDS_0402</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Intake of fresh fruits [g/d]</t>
+          <t>Intake of tree nuts and seeds [g/d]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NUTS_SEEDS_0402</t>
+          <t>MIXEDFRUITS_0403</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Intake of tree nuts and seeds [g/d]</t>
+          <t>Intake of candied fruit/mixed fruit, canned, jarred mixed fruit and miscellaneous fruits [g/d]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIXEDFRUITS_0403</t>
+          <t>OLIVES_0404</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Intake of candied fruit/mixed fruit, canned, jarred mixed fruit and miscellaneous fruits [g/d]</t>
+          <t>Intake of olives [g/d]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OLIVES_0404</t>
+          <t>DAIRY_05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Intake of olives [g/d]</t>
+          <t>Intake of milk and dairy products and milk and milk products (dairy) [g/d]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAIRY_05</t>
+          <t>MILK_0501</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Intake of milk and dairy products and milk and milk products (dairy) [g/d]</t>
+          <t>Intake of (whole) cow and cattle milk [g/d]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MILK_0501</t>
+          <t>MILKBEV_0502</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Intake of (whole) cow and cattle milk [g/d]</t>
+          <t>Intake of buttermilk, traditional buttermilk, flavoured milk, flavoured whey and milk-based drinks (as part-nature) [g/d]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MILKBEV_0502</t>
+          <t>YOGURT_0503</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Intake of buttermilk, traditional buttermilk, flavoured milk, flavoured whey and milk-based drinks (as part-nature) [g/d]</t>
+          <t>Intake of fermented milk products [g/d]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YOGURT_0503</t>
+          <t>CURD_0504</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Intake of fermented milk products [g/d]</t>
+          <t>Intake of cheese curd, quark and cottage [g/d]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CURD_0504</t>
+          <t>CHEESE_0505</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Intake of cheese curd, quark and cottage [g/d]</t>
+          <t>Intake of cheese [g/d]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CHEESE_0505</t>
+          <t>DAIRYDESSERT_0506</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Intake of cheese [g/d]</t>
+          <t>Intake of dairy dessert and similar starchy pudding [g/d]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DAIRYDESSERT_0506</t>
+          <t>CREAM_PROD_0507</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Intake of dairy dessert and similar starchy pudding [g/d]</t>
+          <t>Intake of cream and cream products [g/d]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CREAM_PROD_0507</t>
+          <t>DAIRYCREAM_050701</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Intake of cream and cream products [g/d]</t>
+          <t>Cream intake (as part-nature) [g/d]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DAIRYCREAM_050701</t>
+          <t>NONDAIRYCREAM_050702</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cream intake (as part-nature) [g/d]</t>
+          <t>Intake of imitation cream, non-dairy coffee creamers and dairy imitates other than milk [g/d]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NONDAIRYCREAM_050702</t>
+          <t>CEREAL_PROD_06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Intake of imitation cream, non-dairy coffee creamers and dairy imitates other than milk [g/d]</t>
+          <t>Intake of cereals and cereal primary derivatives, cereal grains (and cereal-like grains) [g/d]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CEREAL_PROD_06</t>
+          <t>PASTA_RICE_0602</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Intake of cereals and cereal primary derivatives, cereal grains (and cereal-like grains) [g/d]</t>
+          <t>Intake of pastas and rice [g/d]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PASTA_RICE_0602</t>
+          <t>BREAD_PROD_0603</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Intake of pastas and rice [g/d]</t>
+          <t>Intake of bread and bread products [g/d]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BREAD_PROD_0603</t>
+          <t>BREAD_060301</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Intake of bread and bread products [g/d]</t>
+          <t>Intake of bread [g/d]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BREAD_060301</t>
+          <t>CRISPBREAD_060302</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Intake of bread [g/d]</t>
+          <t>Intake of crisp bread and rusk [g/d]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CRISPBREAD_060302</t>
+          <t>BREAKF_CEREALS_0604</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Intake of crisp bread and rusk [g/d]</t>
+          <t>Intake of breakfast cereals [g/d]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BREAKF_CEREALS_0604</t>
+          <t>SALT_BISCUIT_0605</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Intake of breakfast cereals [g/d]</t>
+          <t>Intake of crackers and breadsticks [g/d]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SALT_BISCUIT_0605</t>
+          <t>MEAT_PROD_07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Intake of crackers and breadsticks [g/d]</t>
+          <t>Intake of meat and meat products [g/d]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MEAT_PROD_07</t>
+          <t>RED_MEAT_0701</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Intake of meat and meat products [g/d]</t>
+          <t>Intake of red meat (mammals meat) [g/d]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RED_MEAT_0701</t>
+          <t>BEEF_070101</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Intake of red meat (mammals meat) [g/d]</t>
+          <t>Intake of cow, ox or bull fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BEEF_070101</t>
+          <t>VEAL_070102</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Intake of cow, ox or bull fresh meat [g/d]</t>
+          <t>Intake of calf fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VEAL_070102</t>
+          <t>PORK_070103</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Intake of calf fresh meat [g/d]</t>
+          <t>Intake of pig fresh meat [g/d]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PORK_070103</t>
+          <t>MUTTON_LAMB_070104</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Intake of pig fresh meat [g/d]</t>
+          <t>Intake of lamb and sheep meat [g/d]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MUTTON_LAMB_070104</t>
+          <t>POULTRY_0702</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Intake of lamb and sheep meat [g/d]</t>
+          <t>Intake of poultry meat [g/d]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>POULTRY_0702</t>
+          <t>CHICKEN_070201</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Intake of poultry meat [g/d]</t>
+          <t>Intake of chicken meat [g/d]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHICKEN_070201</t>
+          <t>TURKEY_070202</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Intake of chicken meat [g/d]</t>
+          <t>Intake of turkey meat [g/d]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TURKEY_070202</t>
+          <t>DUCK_070203</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Intake of turkey meat [g/d]</t>
+          <t>Intake of duck meat [g/d]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DUCK_070203</t>
+          <t>PROCMEAT_0704</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Intake of duck meat [g/d]</t>
+          <t>Intake of processed or preserved meat [g/d]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PROCMEAT_0704</t>
+          <t>OFFALS_0705</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Intake of processed or preserved meat [g/d]</t>
+          <t>Intake of animal offal and other slaughtering [g/d]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OFFALS_0705</t>
+          <t>FISH_SHELLFISH_08</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Intake of animal offal and other slaughtering [g/d]</t>
+          <t>Intake of fish and seafood and products thereof [g/d]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FISH_SHELLFISH_08</t>
+          <t>FISH_0801</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Intake of fish and seafood and products thereof [g/d]</t>
+          <t>Intake of fish (meat) [g/d]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FISH_0801</t>
+          <t>CRUSTACEANS_0802</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Intake of fish (meat) [g/d]</t>
+          <t>Intake of seafood and products thereof [g/d]</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CRUSTACEANS_0802</t>
+          <t>FISH_PROD_0803</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Intake of seafood and products thereof [g/d]</t>
+          <t>Intake of processed fish [g/d]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FISH_PROD_0803</t>
+          <t>EGG_PROD_09</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Intake of processed fish [g/d]</t>
+          <t>Intake of eggs and egg products [g/d]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EGG_PROD_09</t>
+          <t>FAT_10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Intake of eggs and egg products [g/d]</t>
+          <t>Intake of animal and vegetable fats and oils [g/d]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FAT_10</t>
+          <t>VEGOILS_1001</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Intake of animal and vegetable fats and oils [g/d]</t>
+          <t>Intake of vegetable fats and oils [g/d]</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VEGOILS_1001</t>
+          <t>BUTTER_1002</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Intake of vegetable fats and oils [g/d]</t>
+          <t>Intake of butter [g/d]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BUTTER_1002</t>
+          <t>MARGARINE_1003</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Intake of butter [g/d]</t>
+          <t>Intake of margarines and similar [g/d]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MARGARINE_1003</t>
+          <t>SUGAR_CONFECT_11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Intake of margarines and similar [g/d]</t>
+          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SUGAR_CONFECT_11</t>
+          <t>HONEY_JAM_1101</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
+          <t>Intake of sugars, syrups, honey and table-top sweeteners [g/d]</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HONEY_JAM_1101</t>
+          <t>CHOCOLATE_1102</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Intake of sugars, syrups, honey and table-top sweeteners [g/d]</t>
+          <t>Intake of chocolate, chocolate products and chocolate coated confectionary [g/d]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CHOCOLATE_1102</t>
+          <t>NONCHOC_SWEETS_1103</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Intake of chocolate, chocolate products and chocolate coated confectionary [g/d]</t>
+          <t>Intake of sweet bars and other formed sweet masses, candies (soft and hard) and other confectionery including breath refreshening microsweets [g/d]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NONCHOC_SWEETS_1103</t>
+          <t>ICECREAM_1105</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Intake of sweet bars and other formed sweet masses, candies (soft and hard) and other confectionery including breath refreshening microsweets [g/d]</t>
+          <t>Intake of spoonable desserts and ice creams [g/d]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ICECREAM_1105</t>
+          <t>ICECREAM_MILK_110501</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Intake of spoonable desserts and ice creams [g/d]</t>
+          <t>Intake of milk-based ice cream [g/d]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ICECREAM_MILK_110501</t>
+          <t>SORBET_110502</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Intake of milk-based ice cream [g/d]</t>
+          <t>Sorbet intake [g/d]</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SORBET_110502</t>
+          <t>WATER_ICE_110503</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sorbet intake [g/d]</t>
+          <t>Intake of water-based ice creams [g/d]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WATER_ICE_110503</t>
+          <t>CAKES_12</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Intake of water-based ice creams [g/d]</t>
+          <t>Intake of cakes and fine bakery products [g/d]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CAKES_12</t>
+          <t>NONALC_BEV_13</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Intake of cakes and fine bakery products [g/d]</t>
+          <t>Intake of non-alcoholic beverages [g/d]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NONALC_BEV_13</t>
+          <t>FRUITVEG_JUICE_1301</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Intake of non-alcoholic beverages [g/d]</t>
+          <t>Intake of fruit and vegetable juices [g/d]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRUITVEG_JUICE_1301</t>
+          <t>SOFTDRINKS_1302</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Intake of fruit and vegetable juices [g/d]</t>
+          <t>Intake of soft drinks [g/d]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SOFTDRINKS_1302</t>
+          <t>HOTDRINKS_1303</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Intake of soft drinks [g/d]</t>
+          <t>Intake of hot drinks and similar (coffee, cocoa, tea and herbal infusions) [g/d]</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HOTDRINKS_1303</t>
+          <t>COFFEE_130301</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Intake of hot drinks and similar (coffee, cocoa, tea and herbal infusions) [g/d]</t>
+          <t>Coffee intake [g/d]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>COFFEE_130301</t>
+          <t>TEA_130302</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Coffee intake [g/d]</t>
+          <t>Tea intake [g/d]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TEA_130302</t>
+          <t>HERBALTEA_130303</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tea intake [g/d]</t>
+          <t>Intake of herbal and other non-tea infusions [g/d]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HERBALTEA_130303</t>
+          <t>COFFEE_IMITATE_130304</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Intake of herbal and other non-tea infusions [g/d]</t>
+          <t>Intake of chicory coffee infusion and coffee imitate beverages [g/d]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COFFEE_IMITATE_130304</t>
+          <t>WATER_1304</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Intake of chicory coffee infusion and coffee imitate beverages [g/d]</t>
+          <t>Intake of water and water-based beverages [g/d]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WATER_1304</t>
+          <t>CONDIMENT_SAUCES_15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Intake of water and water-based beverages [g/d]</t>
+          <t>Intake of seasoning, sauces and condiments [g/d]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CONDIMENT_SAUCES_15</t>
+          <t>SAUCES_1501</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Intake of seasoning, sauces and condiments [g/d]</t>
+          <t>Intake of savoury sauces [g/d]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SAUCES_1501</t>
+          <t>TOMATOSAUCE_150101</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Intake of savoury sauces [g/d]</t>
+          <t>Intake of tomato-containing cooked sauces [g/d]</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TOMATOSAUCE_150101</t>
+          <t>DRESSINGS_150102</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Intake of tomato-containing cooked sauces [g/d]</t>
+          <t>Dressing intake [g/d]</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DRESSINGS_150102</t>
+          <t>MAYONNAISE_150103</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dressing intake [g/d]</t>
+          <t>Intake of mayonnaise [g/d]</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MAYONNAISE_150103</t>
+          <t>DESSERTSAUCE_150104</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Intake of mayonnaise [g/d]</t>
+          <t>Intakes of dessert sauces/toppings [g/d]</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DESSERTSAUCE_150104</t>
+          <t>HERBS_SPICES_1503</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Intakes of dessert sauces/toppings [g/d]</t>
+          <t>Intakes of berbs, spices and similar [g/d]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HERBS_SPICES_1503</t>
+          <t>CONDIMENTS_1504</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Intakes of berbs, spices and similar [g/d]</t>
+          <t>Condiments intake [g/d]</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CONDIMENTS_1504</t>
+          <t>SOUP_BOUILLON_16</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Condiments intake [g/d]</t>
+          <t>Intake of soups and broths [g/d]</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SOUP_BOUILLON_16</t>
+          <t>SOUP_1601</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Intake of soups and broths [g/d]</t>
+          <t>Intake of soups [g/d]</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SOUP_1601</t>
+          <t>BOUILLON_1602</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Intake of soups [g/d]</t>
+          <t>Intake of mixed vegetables soup, clear meat soup [g/d]</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BOUILLON_1602</t>
+          <t>MISCELLANEOUS_17</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Intake of mixed vegetables soup, clear meat soup [g/d]</t>
+          <t>Intake of miscellaneous [g/d]</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MISCELLANEOUS_17</t>
+          <t>VEG_DISHES_1700</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Intake of miscellaneous [g/d]</t>
+          <t>Intake of vegetarian products and dishes [g/d]</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VEG_DISHES_1700</t>
+          <t>SOY_PROD_1701</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Intake of vegetarian products and dishes [g/d]</t>
+          <t>Intake of soy products [g/d]</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2283,35 +2283,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SOY_PROD_1701</t>
+          <t>DIET_PROD_1702</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Intake of soy products [g/d]</t>
+          <t>Intake of food for weight reduction [g/d]</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>DIET_PROD_1702</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Intake of food for weight reduction [g/d]</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
